--- a/data/cooking.xlsx
+++ b/data/cooking.xlsx
@@ -42,7 +42,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,21 @@
         <fgColor rgb="FF4F6D7A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6EEF4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -82,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -90,6 +105,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -907,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1735,6 +1753,882 @@
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
     </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>meat_fry</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>고기 튀김</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>item:meat</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>meat</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>fryer</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>고기 획득 시 해금</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>meat_fry</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>meat, meat</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>fryer</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="L21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>meat_fry</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>meat, meat, herb</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>fryer</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="K22" s="7" t="n"/>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>들풀 곁들임</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>meat_stew</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>고기 스튜</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>item:meat</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>meat, potato</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>pot</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>고기 획득 시 해금</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>meat_stew</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>meat, potato, potato, herb</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>pot</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="L24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>meat_stew</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>meat, meat, potato, herb, canned_food</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>pot</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>cheese_salad</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>치즈 들풀 샐러드</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>item:cheese</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>cheese, herb</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>치즈 획득 시 해금</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>cheese_salad</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>cheese, herb, herb</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="L27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>cheese_salad</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr"/>
+      <c r="D28" s="7" t="inlineStr"/>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>cheese, cheese, herb, herb</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K28" s="7" t="n"/>
+      <c r="L28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>cheese_potato</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>치즈 감자</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>item:cheese</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>cheese, potato</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>치즈 획득 시 해금</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>cheese_potato</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="6" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>cheese, potato, potato</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>pot</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>냄비에 녹이기 단계 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>cheese_potato</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr"/>
+      <c r="D31" s="7" t="inlineStr"/>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>cheese, cheese, potato, potato</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>pot</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K31" s="7" t="n"/>
+      <c r="L31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>cheese_meat</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>치즈 고기찜</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>item:meat+cheese</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>meat, cheese</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>pot</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>고기·치즈 둘 다 획득 시 해금</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>cheese_meat</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6" t="inlineStr"/>
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>meat, cheese, potato</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>pot</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="L33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>cheese_meat</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr"/>
+      <c r="D34" s="7" t="inlineStr"/>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>meat, meat, cheese, cheese</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>pot</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>tomato_salad</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>토마토 샐러드</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>item:tomato</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>tomato, herb</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>토마토 획득 시 해금</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>tomato_salad</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>tomato, tomato, herb</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="L36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>tomato_salad</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="7" t="inlineStr"/>
+      <c r="D37" s="7" t="inlineStr"/>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>tomato, tomato, herb, herb</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>tomato_stew</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>토마토 스튜</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>item:tomato</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>tomato, potato</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>pot</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>토마토 획득 시 해금</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>tomato_stew</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6" t="inlineStr"/>
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>tomato, tomato, potato, herb</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>pot</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="L39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>tomato_stew</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr"/>
+      <c r="D40" s="7" t="inlineStr"/>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>tomato, tomato, potato, potato, herb</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>pot</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="K40" s="7" t="n"/>
+      <c r="L40" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cooking.xlsx
+++ b/data/cooking.xlsx
@@ -925,13 +925,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="10"/>
@@ -962,40 +962,45 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>ingredients</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>station</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>timer_seconds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>sat_a</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sat_b</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>sat_c</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>upgrade_mastery</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1020,32 +1025,37 @@
           <t>default</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>herb, canned_food</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>bowl</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="J2" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="K2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>1일차부터 사용 가능</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1058,32 +1068,33 @@
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>herb, herb, canned_food</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>bowl</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="I3" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="L3" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>들풀 추가</t>
         </is>
@@ -1100,30 +1111,31 @@
       </c>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>herb, herb, canned_food, herb</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>bowl</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1141,35 +1153,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>canned_food, herb, canned_food</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>bowl</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="I5" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="J5" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="K5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="L5" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>레시피 북에서 토큰으로 구입</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1182,32 +1201,33 @@
       </c>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>canned_food, herb, canned_food</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="I6" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="K6" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>끓이기 단계 추가</t>
         </is>
@@ -1224,30 +1244,31 @@
       </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>canned_food, herb, canned_food, herb</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="J7" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1268,32 +1289,37 @@
           <t>default</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>herb</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>fryer</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="I8" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="J8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="K8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1일차부터 사용 가능</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1306,32 +1332,33 @@
       </c>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>herb, herb</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>fryer</t>
         </is>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="H9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="K9" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="L9" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1344,30 +1371,31 @@
       </c>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>herb, herb, herb</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>fryer</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="J10" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="K10" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1385,37 +1413,38 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>item:potato</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>potato</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>fryer</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="I11" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="K11" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="L11" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>감자 획득 시 해금</t>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1일차부터 사용 가능</t>
         </is>
       </c>
     </row>
@@ -1430,32 +1459,33 @@
       </c>
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>potato, potato</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>fryer</t>
         </is>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="H12" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="I12" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="J12" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="K12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="L12" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1468,30 +1498,31 @@
       </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>potato, potato, herb</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>fryer</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="K13" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>들풀 시즈닝</t>
         </is>
@@ -1513,37 +1544,40 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>item:potato</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>potato, canned_food</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>bowl</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="I14" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="K14" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="L14" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>감자 획득 시 해금</t>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>레시피 북에서 토큰으로 구입</t>
         </is>
       </c>
     </row>
@@ -1558,32 +1592,33 @@
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>potato, potato, canned_food</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="H15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="I15" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="J15" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="K15" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="L15" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>끓이기 단계 추가</t>
         </is>
@@ -1600,30 +1635,31 @@
       </c>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>potato, potato, canned_food, herb</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="I16" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="J16" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="K16" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1641,37 +1677,40 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>item:potato</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>canned_food, herb, potato</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>bowl</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="I17" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="K17" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="L17" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>감자 획득 시 해금</t>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>레시피 북에서 토큰으로 구입</t>
         </is>
       </c>
     </row>
@@ -1686,32 +1725,33 @@
       </c>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>canned_food, herb, potato, potato</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="H18" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="I18" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="J18" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="K18" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="L18" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>끓이기 단계 추가</t>
         </is>
@@ -1728,30 +1768,31 @@
       </c>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>canned_food, canned_food, herb, potato, potato</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="I19" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="J19" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="K19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1769,37 +1810,40 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>item:meat</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>meat</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>fryer</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="H20" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="I20" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="J20" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="K20" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="L20" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>고기 획득 시 해금</t>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>레시피 북에서 토큰으로 구입</t>
         </is>
       </c>
     </row>
@@ -1814,32 +1858,33 @@
       </c>
       <c r="C21" s="6" t="inlineStr"/>
       <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>meat, meat</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>fryer</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="J21" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="L21" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -1852,30 +1897,31 @@
       </c>
       <c r="C22" s="7" t="inlineStr"/>
       <c r="D22" s="7" t="inlineStr"/>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>meat, meat, herb</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>fryer</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="H22" s="7" t="n">
         <v>5.5</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="I22" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="J22" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="K22" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>들풀 곁들임</t>
         </is>
@@ -1897,37 +1943,40 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>item:meat</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>meat, potato</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="H23" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="I23" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="J23" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="K23" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="K23" s="5" t="n">
+      <c r="L23" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>고기 획득 시 해금</t>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>레시피 북에서 토큰으로 구입</t>
         </is>
       </c>
     </row>
@@ -1942,32 +1991,33 @@
       </c>
       <c r="C24" s="6" t="inlineStr"/>
       <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>meat, potato, potato, herb</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="J24" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="K24" s="6" t="n">
+      <c r="L24" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1980,30 +2030,31 @@
       </c>
       <c r="C25" s="7" t="inlineStr"/>
       <c r="D25" s="7" t="inlineStr"/>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>meat, meat, potato, herb, canned_food</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="H25" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H25" s="7" t="n">
+      <c r="I25" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="J25" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="J25" s="7" t="n">
+      <c r="K25" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2021,37 +2072,40 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>item:cheese</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>cheese, herb</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>bowl</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="H26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="I26" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="J26" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="J26" s="5" t="n">
+      <c r="K26" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K26" s="5" t="n">
+      <c r="L26" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>치즈 획득 시 해금</t>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>레시피 북에서 토큰으로 구입</t>
         </is>
       </c>
     </row>
@@ -2066,32 +2120,33 @@
       </c>
       <c r="C27" s="6" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>cheese, herb, herb</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>bowl</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="J27" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="K27" s="6" t="n">
+      <c r="L27" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="L27" s="6" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -2104,30 +2159,31 @@
       </c>
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="7" t="inlineStr"/>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>cheese, cheese, herb, herb</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>bowl</t>
         </is>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="H28" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="I28" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="J28" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="J28" s="7" t="n">
+      <c r="K28" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="K28" s="7" t="n"/>
-      <c r="L28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="n"/>
+      <c r="M28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2145,37 +2201,40 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>item:cheese</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>cheese, potato</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>bowl</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="H29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="I29" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="J29" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>9</v>
       </c>
       <c r="K29" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>치즈 획득 시 해금</t>
+      <c r="L29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>레시피 북에서 토큰으로 구입</t>
         </is>
       </c>
     </row>
@@ -2190,32 +2249,33 @@
       </c>
       <c r="C30" s="6" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>cheese, potato, potato</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="J30" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="K30" s="6" t="n">
+      <c r="L30" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="L30" s="6" t="inlineStr">
+      <c r="M30" s="6" t="inlineStr">
         <is>
           <t>냄비에 녹이기 단계 추가</t>
         </is>
@@ -2232,30 +2292,31 @@
       </c>
       <c r="C31" s="7" t="inlineStr"/>
       <c r="D31" s="7" t="inlineStr"/>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>cheese, cheese, potato, potato</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="H31" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="H31" s="7" t="n">
+      <c r="I31" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="I31" s="7" t="n">
+      <c r="J31" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="J31" s="7" t="n">
+      <c r="K31" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="K31" s="7" t="n"/>
-      <c r="L31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2273,37 +2334,40 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>item:meat+cheese</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>meat, cheese</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="H32" s="5" t="n">
         <v>4.5</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="I32" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="J32" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>12</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>고기·치즈 둘 다 획득 시 해금</t>
+      <c r="L32" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>레시피 북에서 토큰으로 구입</t>
         </is>
       </c>
     </row>
@@ -2318,32 +2382,33 @@
       </c>
       <c r="C33" s="6" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>meat, cheese, potato</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="J33" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="L33" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="L33" s="6" t="inlineStr"/>
+      <c r="M33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -2356,30 +2421,31 @@
       </c>
       <c r="C34" s="7" t="inlineStr"/>
       <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>meat, meat, cheese, cheese</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="H34" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H34" s="7" t="n">
+      <c r="I34" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="I34" s="7" t="n">
+      <c r="J34" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="J34" s="7" t="n">
+      <c r="K34" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="K34" s="7" t="n"/>
-      <c r="L34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -2397,37 +2463,40 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>item:tomato</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>tomato, herb</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>bowl</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="H35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="I35" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="I35" s="5" t="n">
+      <c r="J35" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="J35" s="5" t="n">
+      <c r="K35" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="L35" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>토마토 획득 시 해금</t>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>레시피 북에서 토큰으로 구입</t>
         </is>
       </c>
     </row>
@@ -2442,32 +2511,33 @@
       </c>
       <c r="C36" s="6" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>tomato, tomato, herb</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>bowl</t>
         </is>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="J36" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="K36" s="6" t="n">
+      <c r="L36" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="L36" s="6" t="inlineStr"/>
+      <c r="M36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -2480,30 +2550,31 @@
       </c>
       <c r="C37" s="7" t="inlineStr"/>
       <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>tomato, tomato, herb, herb</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>bowl</t>
         </is>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="H37" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="7" t="n">
+      <c r="I37" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="I37" s="7" t="n">
+      <c r="J37" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="J37" s="7" t="n">
+      <c r="K37" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="K37" s="7" t="n"/>
-      <c r="L37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2521,37 +2592,40 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>item:tomato</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>tomato, potato</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="H38" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H38" s="5" t="n">
+      <c r="I38" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="I38" s="5" t="n">
+      <c r="J38" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J38" s="5" t="n">
+      <c r="K38" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="K38" s="5" t="n">
+      <c r="L38" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>토마토 획득 시 해금</t>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>레시피 북에서 토큰으로 구입</t>
         </is>
       </c>
     </row>
@@ -2566,32 +2640,33 @@
       </c>
       <c r="C39" s="6" t="inlineStr"/>
       <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>tomato, tomato, potato, herb</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="J39" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="K39" s="6" t="n">
+      <c r="L39" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="L39" s="6" t="inlineStr"/>
+      <c r="M39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -2604,30 +2679,31 @@
       </c>
       <c r="C40" s="7" t="inlineStr"/>
       <c r="D40" s="7" t="inlineStr"/>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>tomato, tomato, potato, potato, herb</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>pot</t>
         </is>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="H40" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="I40" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="I40" s="7" t="n">
+      <c r="J40" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="J40" s="7" t="n">
+      <c r="K40" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="K40" s="7" t="n"/>
-      <c r="L40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="n"/>
+      <c r="M40" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/cooking.xlsx
+++ b/data/cooking.xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ingredients" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recipes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stations" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -41,8 +42,12 @@
       <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +89,11 @@
         <fgColor rgb="00E6EEF4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F6D7A"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -97,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -108,6 +118,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -473,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -666,90 +679,105 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kitchen_helper_bonus</t>
+          <t>server_speed</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.25</v>
+        <v>300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>주방 도우미 배치 시 만족도·토큰 배율</t>
+          <t>서빙 도우미 이동 속도</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>server_speed</t>
+          <t>station_range</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>300</v>
+        <v>36</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>서빙 도우미 이동 속도</t>
+          <t>플레이어 발에서 기구 가장자리까지 이 거리(px) 안이면 상호작용 가능</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>station_range</t>
+          <t>table_slots</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>플레이어 발에서 기구 가장자리까지 이 거리(px) 안이면 상호작용 가능</t>
+          <t>테이블에 올려둘 수 있는 물건(재료·요리) 수</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>table_slots</t>
+          <t>floor_rot_seconds</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>테이블에 올려둘 수 있는 물건(재료·요리) 수</t>
+          <t>바닥에 떨어진 재료·요리가 이 시간(초) 지나면 썩음</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>floor_rot_seconds</t>
+          <t>floor_grade_drop</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>바닥에 떨어진 재료·요리가 이 시간(초) 지나면 썩음</t>
+          <t>바닥에 떨어뜨리면 등급이 이만큼 내려감(A→B→C)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>floor_grade_drop</t>
+          <t>helper_cook_seconds</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>바닥에 떨어뜨리면 등급이 이만큼 내려감(A→B→C)</t>
+          <t>엠마(주방 도우미)가 요리 1개를 만드는 기본 시간(초) — 레시피의 튀김기/냄비 시간이 더해짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>helper_grade</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>엠마가 만든 요리 등급: 1 = A, 2 = B, 3 = C</t>
         </is>
       </c>
     </row>
@@ -2708,4 +2736,151 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>scrap_cost</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>max_count</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>counter</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>조리대</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>기구 배치 화면에서 고철로 구입</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fryer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>튀김기</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pot</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>냄비</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>믹싱볼</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>테이블</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>